--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/1784-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/1784-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A83C84CA-DD99-4F92-AABB-1F73E20311D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C8089DD-F626-4627-A6C9-23A40B2EEE11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{FF939C10-13F9-4CB5-BE36-1ACFF107EF3F}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{9DD910E0-7402-4A9E-8709-CA15F52C185A}"/>
   </bookViews>
   <sheets>
     <sheet name="1784-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1484,25 +1484,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CDFF651-4AFE-4973-9AEC-CE87E874ECFE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88527B73-0FC7-44AF-A481-1E99C2E456B5}">
   <dimension ref="A1:R45"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1530,7 +1530,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1560,7 +1560,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1656,7 +1656,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="37">
         <v>2024</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>26</v>
       </c>
@@ -2042,7 +2042,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2098,7 +2098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="39">
         <v>2023</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>26</v>
       </c>
@@ -2208,7 +2208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>26</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2022</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>26</v>
       </c>
@@ -2430,7 +2430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>26</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>26</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="39">
         <v>2021</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>26</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>26</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>0.41</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>2020</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="39">
         <v>2019</v>
       </c>
@@ -2928,7 +2928,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>26</v>
       </c>
@@ -2984,7 +2984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
         <v>26</v>
       </c>
@@ -3040,7 +3040,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="37">
         <v>2018</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>2017</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="37">
         <v>2016</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="39">
         <v>2015</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="37">
         <v>2014</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="39">
         <v>2013</v>
       </c>
@@ -3364,7 +3364,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
         <v>2012</v>
       </c>
@@ -3418,7 +3418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="39">
         <v>2011</v>
       </c>
@@ -3472,7 +3472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="37">
         <v>2010</v>
       </c>
@@ -3526,7 +3526,7 @@
         <v>3.73</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="39">
         <v>2009</v>
       </c>
@@ -3580,7 +3580,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>2008</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="39">
         <v>2007</v>
       </c>
@@ -3688,7 +3688,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="37">
         <v>2006</v>
       </c>
@@ -3742,7 +3742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="39">
         <v>2005</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="37">
         <v>2004</v>
       </c>
@@ -3850,7 +3850,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="39" t="s">
         <v>47</v>
       </c>
